--- a/Result/profitability/3577.xlsx
+++ b/Result/profitability/3577.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.64</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6900000000000001</v>
+        <v>0.8099999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>54.46625</v>
+        <v>54.86375</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.32</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6237499999999999</v>
+        <v>0.8250000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>53.53625</v>
+        <v>54.57375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.63</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6775</v>
+        <v>0.8075</v>
       </c>
       <c r="N4" t="n">
-        <v>54.565</v>
+        <v>55.2275</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>0.68</v>
       </c>
       <c r="M5" t="n">
-        <v>0.66625</v>
+        <v>0.8262499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>55.11875</v>
+        <v>55.48375</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6025</v>
+        <v>0.77625</v>
       </c>
       <c r="N6" t="n">
-        <v>54.75875</v>
+        <v>55.485</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.04</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5549999999999999</v>
+        <v>0.70125</v>
       </c>
       <c r="N7" t="n">
-        <v>54.68875</v>
+        <v>55.31875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.35</v>
       </c>
       <c r="M8" t="n">
-        <v>0.51875</v>
+        <v>0.56125</v>
       </c>
       <c r="N8" t="n">
-        <v>54.9525</v>
+        <v>54.7925</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3577</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>452</v>
+      </c>
+      <c r="D75" t="n">
+        <v>188</v>
+      </c>
+      <c r="E75" t="n">
+        <v>264</v>
+      </c>
+      <c r="F75" t="n">
+        <v>58.47</v>
+      </c>
+      <c r="G75" t="n">
+        <v>141</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>31.30%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>143</v>
+      </c>
+      <c r="K75" t="n">
+        <v>116</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.83625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>54.81125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2312925170068028</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.280000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02142259414225944</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.415094339622641</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.920000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.05256525652565269</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
